--- a/docs/Mapping_casi_uso/unioni_civili/UnCiv_999.xlsx
+++ b/docs/Mapping_casi_uso/unioni_civili/UnCiv_999.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1309" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="138">
   <si>
     <t>Sezione</t>
   </si>
@@ -117,6 +117,12 @@
   </si>
   <si>
     <t>descrizioneMotivoRecupero</t>
+  </si>
+  <si>
+    <t>Identificativo Atto Cartaceo</t>
+  </si>
+  <si>
+    <t>idAttoCartaceo</t>
   </si>
   <si>
     <t>Data Evento</t>
@@ -478,7 +484,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H187"/>
+  <dimension ref="A1:H188"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="23.58203125" customWidth="true" bestFit="true"/>
@@ -774,13 +780,13 @@
         <v>35</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>37</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>10</v>
@@ -794,16 +800,16 @@
         <v>23</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>10</v>
@@ -817,13 +823,13 @@
         <v>23</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>42</v>
@@ -846,7 +852,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>44</v>
@@ -869,7 +875,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>46</v>
@@ -883,19 +889,19 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="C18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>10</v>
@@ -906,16 +912,16 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>52</v>
@@ -929,16 +935,16 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>54</v>
@@ -952,7 +958,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>55</v>
@@ -961,7 +967,7 @@
         <v>25</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>56</v>
@@ -975,16 +981,16 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>57</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>58</v>
@@ -998,7 +1004,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>59</v>
@@ -1007,7 +1013,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>60</v>
@@ -1021,7 +1027,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>61</v>
@@ -1030,7 +1036,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>62</v>
@@ -1044,16 +1050,16 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>63</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>64</v>
@@ -1067,7 +1073,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>65</v>
@@ -1076,7 +1082,7 @@
         <v>25</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>66</v>
@@ -1090,7 +1096,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>67</v>
@@ -1099,7 +1105,7 @@
         <v>25</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>68</v>
@@ -1113,7 +1119,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>69</v>
@@ -1122,7 +1128,7 @@
         <v>25</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>70</v>
@@ -1136,7 +1142,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>71</v>
@@ -1145,7 +1151,7 @@
         <v>25</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>72</v>
@@ -1159,16 +1165,16 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>74</v>
@@ -1182,7 +1188,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>75</v>
@@ -1191,7 +1197,7 @@
         <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>76</v>
@@ -1205,16 +1211,16 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>77</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>78</v>
@@ -1228,7 +1234,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>79</v>
@@ -1237,7 +1243,7 @@
         <v>25</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>80</v>
@@ -1251,7 +1257,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>81</v>
@@ -1260,7 +1266,7 @@
         <v>25</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>82</v>
@@ -1274,7 +1280,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>83</v>
@@ -1283,7 +1289,7 @@
         <v>25</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>84</v>
@@ -1297,7 +1303,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>85</v>
@@ -1306,7 +1312,7 @@
         <v>25</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>86</v>
@@ -1320,7 +1326,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>87</v>
@@ -1329,7 +1335,7 @@
         <v>25</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>88</v>
@@ -1343,7 +1349,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>89</v>
@@ -1352,7 +1358,7 @@
         <v>25</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>90</v>
@@ -1366,7 +1372,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>91</v>
@@ -1375,7 +1381,7 @@
         <v>25</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>92</v>
@@ -1389,7 +1395,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>93</v>
@@ -1398,7 +1404,7 @@
         <v>25</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>94</v>
@@ -1412,16 +1418,16 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>96</v>
@@ -1435,7 +1441,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>97</v>
@@ -1444,7 +1450,7 @@
         <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>98</v>
@@ -1458,16 +1464,16 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>100</v>
@@ -1481,7 +1487,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>101</v>
@@ -1490,7 +1496,7 @@
         <v>25</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>102</v>
@@ -1504,7 +1510,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>103</v>
@@ -1513,7 +1519,7 @@
         <v>25</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>104</v>
@@ -1527,7 +1533,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>105</v>
@@ -1536,7 +1542,7 @@
         <v>25</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>106</v>
@@ -1550,7 +1556,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>107</v>
@@ -1559,7 +1565,7 @@
         <v>25</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>108</v>
@@ -1573,19 +1579,19 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B48" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="C48" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D48" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E48" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>10</v>
@@ -1596,16 +1602,16 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>52</v>
@@ -1619,16 +1625,16 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>54</v>
@@ -1642,7 +1648,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>55</v>
@@ -1651,7 +1657,7 @@
         <v>25</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>56</v>
@@ -1665,16 +1671,16 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>57</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>58</v>
@@ -1688,7 +1694,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>59</v>
@@ -1697,7 +1703,7 @@
         <v>9</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>60</v>
@@ -1711,7 +1717,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>61</v>
@@ -1720,7 +1726,7 @@
         <v>9</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>62</v>
@@ -1734,16 +1740,16 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>63</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>64</v>
@@ -1757,7 +1763,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>65</v>
@@ -1766,7 +1772,7 @@
         <v>25</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>66</v>
@@ -1780,7 +1786,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>67</v>
@@ -1789,7 +1795,7 @@
         <v>25</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>68</v>
@@ -1803,7 +1809,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>69</v>
@@ -1812,7 +1818,7 @@
         <v>25</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>70</v>
@@ -1826,7 +1832,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>71</v>
@@ -1835,7 +1841,7 @@
         <v>25</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>72</v>
@@ -1849,16 +1855,16 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>74</v>
@@ -1872,7 +1878,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>75</v>
@@ -1881,7 +1887,7 @@
         <v>9</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>76</v>
@@ -1895,16 +1901,16 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>77</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>78</v>
@@ -1918,7 +1924,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>79</v>
@@ -1927,7 +1933,7 @@
         <v>25</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>80</v>
@@ -1941,7 +1947,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>81</v>
@@ -1950,7 +1956,7 @@
         <v>25</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>82</v>
@@ -1964,7 +1970,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>83</v>
@@ -1973,7 +1979,7 @@
         <v>25</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>84</v>
@@ -1987,7 +1993,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>85</v>
@@ -1996,7 +2002,7 @@
         <v>25</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>86</v>
@@ -2010,7 +2016,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>87</v>
@@ -2019,7 +2025,7 @@
         <v>25</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>88</v>
@@ -2033,7 +2039,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>89</v>
@@ -2042,7 +2048,7 @@
         <v>25</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>90</v>
@@ -2056,7 +2062,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>91</v>
@@ -2065,7 +2071,7 @@
         <v>25</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>92</v>
@@ -2079,7 +2085,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>93</v>
@@ -2088,7 +2094,7 @@
         <v>25</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>94</v>
@@ -2102,16 +2108,16 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>96</v>
@@ -2125,7 +2131,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>97</v>
@@ -2134,7 +2140,7 @@
         <v>9</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>98</v>
@@ -2148,16 +2154,16 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>100</v>
@@ -2171,7 +2177,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>101</v>
@@ -2180,7 +2186,7 @@
         <v>25</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>102</v>
@@ -2194,7 +2200,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>103</v>
@@ -2203,7 +2209,7 @@
         <v>25</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>104</v>
@@ -2217,7 +2223,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>105</v>
@@ -2226,7 +2232,7 @@
         <v>25</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>106</v>
@@ -2240,7 +2246,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>107</v>
@@ -2249,7 +2255,7 @@
         <v>25</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>108</v>
@@ -2266,7 +2272,7 @@
         <v>111</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>48</v>
+        <v>109</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>25</v>
@@ -2275,27 +2281,27 @@
         <v>112</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>113</v>
+        <v>16</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>52</v>
@@ -2304,21 +2310,21 @@
         <v>10</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>54</v>
@@ -2327,21 +2333,21 @@
         <v>10</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>56</v>
@@ -2350,12 +2356,12 @@
         <v>10</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>57</v>
@@ -2364,7 +2370,7 @@
         <v>9</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>58</v>
@@ -2373,12 +2379,12 @@
         <v>10</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>59</v>
@@ -2387,7 +2393,7 @@
         <v>9</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>60</v>
@@ -2396,12 +2402,12 @@
         <v>10</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>61</v>
@@ -2410,7 +2416,7 @@
         <v>9</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>62</v>
@@ -2419,21 +2425,21 @@
         <v>10</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>63</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>64</v>
@@ -2442,12 +2448,12 @@
         <v>10</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>65</v>
@@ -2456,7 +2462,7 @@
         <v>25</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>66</v>
@@ -2465,12 +2471,12 @@
         <v>10</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>67</v>
@@ -2479,7 +2485,7 @@
         <v>25</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>68</v>
@@ -2488,12 +2494,12 @@
         <v>10</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>69</v>
@@ -2502,7 +2508,7 @@
         <v>25</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>70</v>
@@ -2511,12 +2517,12 @@
         <v>10</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>71</v>
@@ -2525,7 +2531,7 @@
         <v>25</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>72</v>
@@ -2534,12 +2540,12 @@
         <v>10</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>73</v>
@@ -2548,7 +2554,7 @@
         <v>25</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>74</v>
@@ -2557,12 +2563,12 @@
         <v>10</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>75</v>
@@ -2571,7 +2577,7 @@
         <v>25</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>76</v>
@@ -2580,12 +2586,12 @@
         <v>10</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>77</v>
@@ -2594,7 +2600,7 @@
         <v>25</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>78</v>
@@ -2603,12 +2609,12 @@
         <v>10</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>79</v>
@@ -2617,7 +2623,7 @@
         <v>25</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>80</v>
@@ -2626,12 +2632,12 @@
         <v>10</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>81</v>
@@ -2640,7 +2646,7 @@
         <v>25</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>82</v>
@@ -2649,12 +2655,12 @@
         <v>10</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>83</v>
@@ -2663,7 +2669,7 @@
         <v>25</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>84</v>
@@ -2672,12 +2678,12 @@
         <v>10</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>85</v>
@@ -2686,7 +2692,7 @@
         <v>25</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>86</v>
@@ -2695,12 +2701,12 @@
         <v>10</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>87</v>
@@ -2709,7 +2715,7 @@
         <v>25</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>88</v>
@@ -2718,12 +2724,12 @@
         <v>10</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>89</v>
@@ -2732,7 +2738,7 @@
         <v>25</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>90</v>
@@ -2741,12 +2747,12 @@
         <v>10</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>91</v>
@@ -2755,7 +2761,7 @@
         <v>25</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>92</v>
@@ -2764,12 +2770,12 @@
         <v>10</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>93</v>
@@ -2778,7 +2784,7 @@
         <v>25</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>94</v>
@@ -2787,21 +2793,21 @@
         <v>10</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>96</v>
@@ -2810,12 +2816,12 @@
         <v>10</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>97</v>
@@ -2824,7 +2830,7 @@
         <v>9</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>98</v>
@@ -2833,21 +2839,21 @@
         <v>10</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>100</v>
@@ -2856,44 +2862,44 @@
         <v>10</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D104" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B104" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D104" s="2" t="s">
+      <c r="E104" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G104" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="E104" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F104" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G104" s="2" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>52</v>
@@ -2902,21 +2908,21 @@
         <v>10</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>54</v>
@@ -2925,21 +2931,21 @@
         <v>10</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>56</v>
@@ -2948,12 +2954,12 @@
         <v>10</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>57</v>
@@ -2962,7 +2968,7 @@
         <v>9</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>58</v>
@@ -2971,12 +2977,12 @@
         <v>10</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>59</v>
@@ -2985,7 +2991,7 @@
         <v>9</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>60</v>
@@ -2994,12 +3000,12 @@
         <v>10</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>61</v>
@@ -3008,7 +3014,7 @@
         <v>9</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>62</v>
@@ -3017,21 +3023,21 @@
         <v>10</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>63</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>64</v>
@@ -3040,12 +3046,12 @@
         <v>10</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>65</v>
@@ -3054,7 +3060,7 @@
         <v>25</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>66</v>
@@ -3063,12 +3069,12 @@
         <v>10</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>67</v>
@@ -3077,7 +3083,7 @@
         <v>25</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>68</v>
@@ -3086,12 +3092,12 @@
         <v>10</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>69</v>
@@ -3100,7 +3106,7 @@
         <v>25</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>70</v>
@@ -3109,12 +3115,12 @@
         <v>10</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>71</v>
@@ -3123,7 +3129,7 @@
         <v>25</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>72</v>
@@ -3132,12 +3138,12 @@
         <v>10</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>73</v>
@@ -3146,7 +3152,7 @@
         <v>25</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>74</v>
@@ -3155,12 +3161,12 @@
         <v>10</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>75</v>
@@ -3169,7 +3175,7 @@
         <v>25</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>76</v>
@@ -3178,12 +3184,12 @@
         <v>10</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>77</v>
@@ -3192,7 +3198,7 @@
         <v>25</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>78</v>
@@ -3201,12 +3207,12 @@
         <v>10</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>79</v>
@@ -3215,7 +3221,7 @@
         <v>25</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>80</v>
@@ -3224,12 +3230,12 @@
         <v>10</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>81</v>
@@ -3238,7 +3244,7 @@
         <v>25</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>82</v>
@@ -3247,12 +3253,12 @@
         <v>10</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>83</v>
@@ -3261,7 +3267,7 @@
         <v>25</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>84</v>
@@ -3270,12 +3276,12 @@
         <v>10</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>85</v>
@@ -3284,7 +3290,7 @@
         <v>25</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>86</v>
@@ -3293,12 +3299,12 @@
         <v>10</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>87</v>
@@ -3307,7 +3313,7 @@
         <v>25</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>88</v>
@@ -3316,12 +3322,12 @@
         <v>10</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>89</v>
@@ -3330,7 +3336,7 @@
         <v>25</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>90</v>
@@ -3339,12 +3345,12 @@
         <v>10</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>91</v>
@@ -3353,7 +3359,7 @@
         <v>25</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>92</v>
@@ -3362,12 +3368,12 @@
         <v>10</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>93</v>
@@ -3376,7 +3382,7 @@
         <v>25</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>94</v>
@@ -3385,21 +3391,21 @@
         <v>10</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>96</v>
@@ -3408,12 +3414,12 @@
         <v>10</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>97</v>
@@ -3422,7 +3428,7 @@
         <v>9</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>98</v>
@@ -3431,21 +3437,21 @@
         <v>10</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>100</v>
@@ -3454,44 +3460,44 @@
         <v>10</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D130" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B130" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C130" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D130" s="2" t="s">
+      <c r="E130" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F130" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G130" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="E130" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F130" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G130" s="2" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>52</v>
@@ -3500,21 +3506,21 @@
         <v>10</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>54</v>
@@ -3523,21 +3529,21 @@
         <v>10</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>56</v>
@@ -3546,12 +3552,12 @@
         <v>10</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>57</v>
@@ -3560,7 +3566,7 @@
         <v>9</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>58</v>
@@ -3569,12 +3575,12 @@
         <v>10</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>59</v>
@@ -3583,7 +3589,7 @@
         <v>9</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>60</v>
@@ -3592,12 +3598,12 @@
         <v>10</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>61</v>
@@ -3606,7 +3612,7 @@
         <v>9</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>62</v>
@@ -3615,21 +3621,21 @@
         <v>10</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>63</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>64</v>
@@ -3638,12 +3644,12 @@
         <v>10</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>65</v>
@@ -3652,7 +3658,7 @@
         <v>25</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>66</v>
@@ -3661,12 +3667,12 @@
         <v>10</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>67</v>
@@ -3675,7 +3681,7 @@
         <v>25</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>68</v>
@@ -3684,12 +3690,12 @@
         <v>10</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>69</v>
@@ -3698,7 +3704,7 @@
         <v>25</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>70</v>
@@ -3707,12 +3713,12 @@
         <v>10</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>71</v>
@@ -3721,7 +3727,7 @@
         <v>25</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>72</v>
@@ -3730,12 +3736,12 @@
         <v>10</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>73</v>
@@ -3744,7 +3750,7 @@
         <v>25</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>74</v>
@@ -3753,12 +3759,12 @@
         <v>10</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>75</v>
@@ -3767,7 +3773,7 @@
         <v>25</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>76</v>
@@ -3776,12 +3782,12 @@
         <v>10</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>77</v>
@@ -3790,7 +3796,7 @@
         <v>25</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>78</v>
@@ -3799,12 +3805,12 @@
         <v>10</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>79</v>
@@ -3813,7 +3819,7 @@
         <v>25</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>80</v>
@@ -3822,12 +3828,12 @@
         <v>10</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>81</v>
@@ -3836,7 +3842,7 @@
         <v>25</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>82</v>
@@ -3845,12 +3851,12 @@
         <v>10</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B147" s="2" t="s">
         <v>83</v>
@@ -3859,7 +3865,7 @@
         <v>25</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>84</v>
@@ -3868,12 +3874,12 @@
         <v>10</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B148" s="2" t="s">
         <v>85</v>
@@ -3882,7 +3888,7 @@
         <v>25</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>86</v>
@@ -3891,12 +3897,12 @@
         <v>10</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>87</v>
@@ -3905,7 +3911,7 @@
         <v>25</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>88</v>
@@ -3914,12 +3920,12 @@
         <v>10</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B150" s="2" t="s">
         <v>89</v>
@@ -3928,7 +3934,7 @@
         <v>25</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>90</v>
@@ -3937,12 +3943,12 @@
         <v>10</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B151" s="2" t="s">
         <v>91</v>
@@ -3951,7 +3957,7 @@
         <v>25</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>92</v>
@@ -3960,12 +3966,12 @@
         <v>10</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B152" s="2" t="s">
         <v>93</v>
@@ -3974,7 +3980,7 @@
         <v>25</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>94</v>
@@ -3983,21 +3989,21 @@
         <v>10</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B153" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E153" s="2" t="s">
         <v>96</v>
@@ -4006,12 +4012,12 @@
         <v>10</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B154" s="2" t="s">
         <v>97</v>
@@ -4020,7 +4026,7 @@
         <v>9</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>98</v>
@@ -4029,21 +4035,21 @@
         <v>10</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B155" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>100</v>
@@ -4052,44 +4058,44 @@
         <v>10</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D156" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B156" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C156" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D156" s="2" t="s">
+      <c r="E156" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F156" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G156" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="E156" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F156" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G156" s="2" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>52</v>
@@ -4098,21 +4104,21 @@
         <v>10</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B158" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>54</v>
@@ -4121,21 +4127,21 @@
         <v>10</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B159" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E159" s="2" t="s">
         <v>56</v>
@@ -4144,12 +4150,12 @@
         <v>10</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B160" s="2" t="s">
         <v>57</v>
@@ -4158,7 +4164,7 @@
         <v>9</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>58</v>
@@ -4167,12 +4173,12 @@
         <v>10</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B161" s="2" t="s">
         <v>59</v>
@@ -4181,7 +4187,7 @@
         <v>9</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E161" s="2" t="s">
         <v>60</v>
@@ -4190,12 +4196,12 @@
         <v>10</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>61</v>
@@ -4204,7 +4210,7 @@
         <v>9</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>62</v>
@@ -4213,21 +4219,21 @@
         <v>10</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B163" s="2" t="s">
         <v>63</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>64</v>
@@ -4236,12 +4242,12 @@
         <v>10</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B164" s="2" t="s">
         <v>65</v>
@@ -4250,7 +4256,7 @@
         <v>25</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>66</v>
@@ -4259,12 +4265,12 @@
         <v>10</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B165" s="2" t="s">
         <v>67</v>
@@ -4273,7 +4279,7 @@
         <v>25</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E165" s="2" t="s">
         <v>68</v>
@@ -4282,12 +4288,12 @@
         <v>10</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B166" s="2" t="s">
         <v>69</v>
@@ -4296,7 +4302,7 @@
         <v>25</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E166" s="2" t="s">
         <v>70</v>
@@ -4305,12 +4311,12 @@
         <v>10</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B167" s="2" t="s">
         <v>71</v>
@@ -4319,7 +4325,7 @@
         <v>25</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E167" s="2" t="s">
         <v>72</v>
@@ -4328,12 +4334,12 @@
         <v>10</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B168" s="2" t="s">
         <v>73</v>
@@ -4342,7 +4348,7 @@
         <v>25</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E168" s="2" t="s">
         <v>74</v>
@@ -4351,12 +4357,12 @@
         <v>10</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B169" s="2" t="s">
         <v>75</v>
@@ -4365,7 +4371,7 @@
         <v>25</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E169" s="2" t="s">
         <v>76</v>
@@ -4374,12 +4380,12 @@
         <v>10</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B170" s="2" t="s">
         <v>77</v>
@@ -4388,7 +4394,7 @@
         <v>25</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>78</v>
@@ -4397,12 +4403,12 @@
         <v>10</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B171" s="2" t="s">
         <v>79</v>
@@ -4411,7 +4417,7 @@
         <v>25</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E171" s="2" t="s">
         <v>80</v>
@@ -4420,12 +4426,12 @@
         <v>10</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B172" s="2" t="s">
         <v>81</v>
@@ -4434,7 +4440,7 @@
         <v>25</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E172" s="2" t="s">
         <v>82</v>
@@ -4443,12 +4449,12 @@
         <v>10</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B173" s="2" t="s">
         <v>83</v>
@@ -4457,7 +4463,7 @@
         <v>25</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E173" s="2" t="s">
         <v>84</v>
@@ -4466,12 +4472,12 @@
         <v>10</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B174" s="2" t="s">
         <v>85</v>
@@ -4480,7 +4486,7 @@
         <v>25</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E174" s="2" t="s">
         <v>86</v>
@@ -4489,12 +4495,12 @@
         <v>10</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B175" s="2" t="s">
         <v>87</v>
@@ -4503,7 +4509,7 @@
         <v>25</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E175" s="2" t="s">
         <v>88</v>
@@ -4512,12 +4518,12 @@
         <v>10</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B176" s="2" t="s">
         <v>89</v>
@@ -4526,7 +4532,7 @@
         <v>25</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>90</v>
@@ -4535,12 +4541,12 @@
         <v>10</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B177" s="2" t="s">
         <v>91</v>
@@ -4549,7 +4555,7 @@
         <v>25</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E177" s="2" t="s">
         <v>92</v>
@@ -4558,12 +4564,12 @@
         <v>10</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B178" s="2" t="s">
         <v>93</v>
@@ -4572,7 +4578,7 @@
         <v>25</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E178" s="2" t="s">
         <v>94</v>
@@ -4581,21 +4587,21 @@
         <v>10</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B179" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E179" s="2" t="s">
         <v>96</v>
@@ -4604,12 +4610,12 @@
         <v>10</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B180" s="2" t="s">
         <v>97</v>
@@ -4618,7 +4624,7 @@
         <v>9</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E180" s="2" t="s">
         <v>98</v>
@@ -4627,21 +4633,21 @@
         <v>10</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B181" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E181" s="2" t="s">
         <v>100</v>
@@ -4650,30 +4656,30 @@
         <v>10</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C182" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D182" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B182" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C182" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D182" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="E182" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F182" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G182" s="2" t="s">
         <v>124</v>
-      </c>
-      <c r="F182" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G182" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="183">
@@ -4681,16 +4687,16 @@
         <v>125</v>
       </c>
       <c r="B183" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C183" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D183" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E183" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="C183" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D183" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E183" s="2" t="s">
-        <v>127</v>
       </c>
       <c r="F183" s="2" t="s">
         <v>10</v>
@@ -4701,19 +4707,19 @@
     </row>
     <row r="184">
       <c r="A184" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B184" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B184" s="2" t="s">
+      <c r="C184" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D184" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E184" s="2" t="s">
         <v>129</v>
-      </c>
-      <c r="C184" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D184" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="E184" s="2" t="s">
-        <v>131</v>
       </c>
       <c r="F184" s="2" t="s">
         <v>10</v>
@@ -4724,16 +4730,16 @@
     </row>
     <row r="185">
       <c r="A185" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B185" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C185" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D185" s="2" t="s">
         <v>132</v>
-      </c>
-      <c r="C185" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D185" s="2" t="s">
-        <v>130</v>
       </c>
       <c r="E185" s="2" t="s">
         <v>133</v>
@@ -4747,7 +4753,7 @@
     </row>
     <row r="186">
       <c r="A186" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B186" s="2" t="s">
         <v>134</v>
@@ -4756,7 +4762,7 @@
         <v>25</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E186" s="2" t="s">
         <v>135</v>
@@ -4770,24 +4776,47 @@
     </row>
     <row r="187">
       <c r="A187" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B187" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C187" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D187" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E187" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F187" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G187" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B188" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C187" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D187" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="E187" s="2" t="s">
+      <c r="C188" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D188" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E188" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F187" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G187" s="2" t="s">
+      <c r="F188" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G188" s="2" t="s">
         <v>16</v>
       </c>
     </row>

--- a/docs/Mapping_casi_uso/unioni_civili/UnCiv_999.xlsx
+++ b/docs/Mapping_casi_uso/unioni_civili/UnCiv_999.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1400" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1407" uniqueCount="144">
   <si>
     <t>Sezione</t>
   </si>
@@ -35,6 +35,18 @@
     <t>Condizioni obbligatorieta'</t>
   </si>
   <si>
+    <t>Allegati</t>
+  </si>
+  <si>
+    <t>Allegato generico</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
     <t>Formula</t>
   </si>
   <si>
@@ -44,9 +56,6 @@
     <t>SI</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Si puo' ignorare la sezione per</t>
   </si>
   <si>
@@ -87,9 +96,6 @@
   </si>
   <si>
     <t>Data decorrenza</t>
-  </si>
-  <si>
-    <t>NO</t>
   </si>
   <si>
     <t>dataDecorrenza</t>
@@ -496,7 +502,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H200"/>
+  <dimension ref="A1:H201"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="23.58203125" customWidth="true" bestFit="true"/>
@@ -555,63 +561,63 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="G4" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>18</v>
@@ -620,90 +626,90 @@
         <v>10</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="F8" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>28</v>
@@ -712,21 +718,21 @@
         <v>10</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>30</v>
@@ -735,12 +741,12 @@
         <v>10</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>31</v>
@@ -749,7 +755,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>32</v>
@@ -758,21 +764,21 @@
         <v>10</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>34</v>
@@ -781,21 +787,21 @@
         <v>10</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>36</v>
@@ -804,12 +810,12 @@
         <v>10</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>37</v>
@@ -818,53 +824,53 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="F14" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="F15" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>44</v>
@@ -873,21 +879,21 @@
         <v>10</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>46</v>
@@ -896,21 +902,21 @@
         <v>10</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>47</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>48</v>
@@ -919,44 +925,44 @@
         <v>10</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="C19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="F19" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>54</v>
@@ -965,21 +971,21 @@
         <v>10</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>56</v>
@@ -988,21 +994,21 @@
         <v>10</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>57</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>58</v>
@@ -1011,21 +1017,21 @@
         <v>10</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>59</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>60</v>
@@ -1034,21 +1040,21 @@
         <v>10</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>61</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>62</v>
@@ -1057,12 +1063,12 @@
         <v>10</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>63</v>
@@ -1071,7 +1077,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>64</v>
@@ -1080,21 +1086,21 @@
         <v>10</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>66</v>
@@ -1103,21 +1109,21 @@
         <v>10</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>68</v>
@@ -1126,21 +1132,21 @@
         <v>10</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>70</v>
@@ -1149,21 +1155,21 @@
         <v>10</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>71</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>72</v>
@@ -1172,21 +1178,21 @@
         <v>10</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>74</v>
@@ -1195,21 +1201,21 @@
         <v>10</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>75</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>76</v>
@@ -1218,21 +1224,21 @@
         <v>10</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>77</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>78</v>
@@ -1241,12 +1247,12 @@
         <v>10</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>79</v>
@@ -1255,7 +1261,7 @@
         <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>80</v>
@@ -1264,21 +1270,21 @@
         <v>10</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>82</v>
@@ -1287,21 +1293,21 @@
         <v>10</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>83</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>84</v>
@@ -1310,21 +1316,21 @@
         <v>10</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>85</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>86</v>
@@ -1333,21 +1339,21 @@
         <v>10</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>88</v>
@@ -1356,21 +1362,21 @@
         <v>10</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>89</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>90</v>
@@ -1379,21 +1385,21 @@
         <v>10</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>92</v>
@@ -1402,21 +1408,21 @@
         <v>10</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>93</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>94</v>
@@ -1425,21 +1431,21 @@
         <v>10</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>96</v>
@@ -1448,21 +1454,21 @@
         <v>10</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>98</v>
@@ -1471,21 +1477,21 @@
         <v>10</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>100</v>
@@ -1494,12 +1500,12 @@
         <v>10</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>101</v>
@@ -1508,7 +1514,7 @@
         <v>9</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>102</v>
@@ -1517,21 +1523,21 @@
         <v>10</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>103</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>104</v>
@@ -1540,21 +1546,21 @@
         <v>10</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>105</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>106</v>
@@ -1563,21 +1569,21 @@
         <v>10</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>107</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>108</v>
@@ -1586,21 +1592,21 @@
         <v>10</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>109</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>110</v>
@@ -1609,21 +1615,21 @@
         <v>10</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>111</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>112</v>
@@ -1632,21 +1638,21 @@
         <v>10</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>113</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>114</v>
@@ -1655,44 +1661,44 @@
         <v>10</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B51" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>50</v>
-      </c>
       <c r="C51" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D51" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E51" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E51" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="F51" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>54</v>
@@ -1701,21 +1707,21 @@
         <v>10</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>56</v>
@@ -1724,21 +1730,21 @@
         <v>10</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>57</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>58</v>
@@ -1747,21 +1753,21 @@
         <v>10</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>59</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>60</v>
@@ -1770,21 +1776,21 @@
         <v>10</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>61</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>62</v>
@@ -1793,12 +1799,12 @@
         <v>10</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>63</v>
@@ -1807,7 +1813,7 @@
         <v>9</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>64</v>
@@ -1816,21 +1822,21 @@
         <v>10</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>66</v>
@@ -1839,21 +1845,21 @@
         <v>10</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>68</v>
@@ -1862,21 +1868,21 @@
         <v>10</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>70</v>
@@ -1885,21 +1891,21 @@
         <v>10</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>71</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>72</v>
@@ -1908,21 +1914,21 @@
         <v>10</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>74</v>
@@ -1931,21 +1937,21 @@
         <v>10</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>75</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>76</v>
@@ -1954,21 +1960,21 @@
         <v>10</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>77</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>78</v>
@@ -1977,12 +1983,12 @@
         <v>10</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>79</v>
@@ -1991,7 +1997,7 @@
         <v>9</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>80</v>
@@ -2000,21 +2006,21 @@
         <v>10</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>82</v>
@@ -2023,21 +2029,21 @@
         <v>10</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>83</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>84</v>
@@ -2046,21 +2052,21 @@
         <v>10</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>85</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>86</v>
@@ -2069,21 +2075,21 @@
         <v>10</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>88</v>
@@ -2092,21 +2098,21 @@
         <v>10</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>89</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>90</v>
@@ -2115,21 +2121,21 @@
         <v>10</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>92</v>
@@ -2138,21 +2144,21 @@
         <v>10</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>93</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>94</v>
@@ -2161,21 +2167,21 @@
         <v>10</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>96</v>
@@ -2184,21 +2190,21 @@
         <v>10</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>98</v>
@@ -2207,21 +2213,21 @@
         <v>10</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>100</v>
@@ -2230,12 +2236,12 @@
         <v>10</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>101</v>
@@ -2244,7 +2250,7 @@
         <v>9</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>102</v>
@@ -2253,21 +2259,21 @@
         <v>10</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>103</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>104</v>
@@ -2276,21 +2282,21 @@
         <v>10</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>105</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>106</v>
@@ -2299,21 +2305,21 @@
         <v>10</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>107</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>108</v>
@@ -2322,21 +2328,21 @@
         <v>10</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>109</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>110</v>
@@ -2345,21 +2351,21 @@
         <v>10</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>111</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>112</v>
@@ -2368,21 +2374,21 @@
         <v>10</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>113</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>114</v>
@@ -2391,7 +2397,7 @@
         <v>10</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="83">
@@ -2399,36 +2405,36 @@
         <v>117</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>50</v>
+        <v>115</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>118</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>52</v>
+        <v>116</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>119</v>
+        <v>19</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>54</v>
@@ -2437,21 +2443,21 @@
         <v>10</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>56</v>
@@ -2460,12 +2466,12 @@
         <v>10</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>57</v>
@@ -2474,7 +2480,7 @@
         <v>9</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>58</v>
@@ -2483,21 +2489,21 @@
         <v>10</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>59</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>60</v>
@@ -2506,21 +2512,21 @@
         <v>10</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>61</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>62</v>
@@ -2529,12 +2535,12 @@
         <v>10</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>63</v>
@@ -2543,7 +2549,7 @@
         <v>9</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>64</v>
@@ -2552,21 +2558,21 @@
         <v>10</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>66</v>
@@ -2575,21 +2581,21 @@
         <v>10</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>68</v>
@@ -2598,21 +2604,21 @@
         <v>10</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>70</v>
@@ -2621,21 +2627,21 @@
         <v>10</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>71</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>72</v>
@@ -2644,21 +2650,21 @@
         <v>10</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>74</v>
@@ -2667,21 +2673,21 @@
         <v>10</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>75</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>76</v>
@@ -2690,21 +2696,21 @@
         <v>10</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>77</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>78</v>
@@ -2713,21 +2719,21 @@
         <v>10</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>80</v>
@@ -2736,21 +2742,21 @@
         <v>10</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>82</v>
@@ -2759,21 +2765,21 @@
         <v>10</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>83</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>84</v>
@@ -2782,21 +2788,21 @@
         <v>10</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>85</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>86</v>
@@ -2805,21 +2811,21 @@
         <v>10</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>88</v>
@@ -2828,21 +2834,21 @@
         <v>10</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>89</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>90</v>
@@ -2851,21 +2857,21 @@
         <v>10</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>92</v>
@@ -2874,21 +2880,21 @@
         <v>10</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>93</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>94</v>
@@ -2897,21 +2903,21 @@
         <v>10</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>96</v>
@@ -2920,21 +2926,21 @@
         <v>10</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>98</v>
@@ -2943,21 +2949,21 @@
         <v>10</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>100</v>
@@ -2966,12 +2972,12 @@
         <v>10</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>101</v>
@@ -2980,7 +2986,7 @@
         <v>9</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>102</v>
@@ -2989,21 +2995,21 @@
         <v>10</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>103</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>104</v>
@@ -3012,21 +3018,21 @@
         <v>10</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>105</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>106</v>
@@ -3035,44 +3041,44 @@
         <v>10</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D111" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B111" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C111" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D111" s="2" t="s">
+      <c r="E111" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G111" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="E111" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F111" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G111" s="2" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>54</v>
@@ -3081,21 +3087,21 @@
         <v>10</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>56</v>
@@ -3104,12 +3110,12 @@
         <v>10</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>57</v>
@@ -3118,7 +3124,7 @@
         <v>9</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>58</v>
@@ -3127,21 +3133,21 @@
         <v>10</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>59</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>60</v>
@@ -3150,21 +3156,21 @@
         <v>10</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>61</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>62</v>
@@ -3173,12 +3179,12 @@
         <v>10</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>63</v>
@@ -3187,7 +3193,7 @@
         <v>9</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>64</v>
@@ -3196,21 +3202,21 @@
         <v>10</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>66</v>
@@ -3219,21 +3225,21 @@
         <v>10</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>68</v>
@@ -3242,21 +3248,21 @@
         <v>10</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>70</v>
@@ -3265,21 +3271,21 @@
         <v>10</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>71</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>72</v>
@@ -3288,21 +3294,21 @@
         <v>10</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>74</v>
@@ -3311,21 +3317,21 @@
         <v>10</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>75</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>76</v>
@@ -3334,21 +3340,21 @@
         <v>10</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>77</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>78</v>
@@ -3357,21 +3363,21 @@
         <v>10</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>80</v>
@@ -3380,21 +3386,21 @@
         <v>10</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>82</v>
@@ -3403,21 +3409,21 @@
         <v>10</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>83</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>84</v>
@@ -3426,21 +3432,21 @@
         <v>10</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>85</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>86</v>
@@ -3449,21 +3455,21 @@
         <v>10</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>88</v>
@@ -3472,21 +3478,21 @@
         <v>10</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>89</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>90</v>
@@ -3495,21 +3501,21 @@
         <v>10</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>92</v>
@@ -3518,21 +3524,21 @@
         <v>10</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>93</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>94</v>
@@ -3541,21 +3547,21 @@
         <v>10</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>96</v>
@@ -3564,21 +3570,21 @@
         <v>10</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>98</v>
@@ -3587,21 +3593,21 @@
         <v>10</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>100</v>
@@ -3610,12 +3616,12 @@
         <v>10</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>101</v>
@@ -3624,7 +3630,7 @@
         <v>9</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>102</v>
@@ -3633,21 +3639,21 @@
         <v>10</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>103</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>104</v>
@@ -3656,21 +3662,21 @@
         <v>10</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>105</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>106</v>
@@ -3679,44 +3685,44 @@
         <v>10</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D139" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B139" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C139" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D139" s="2" t="s">
+      <c r="E139" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F139" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G139" s="2" t="s">
         <v>124</v>
-      </c>
-      <c r="E139" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F139" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G139" s="2" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>54</v>
@@ -3725,21 +3731,21 @@
         <v>10</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>56</v>
@@ -3748,12 +3754,12 @@
         <v>10</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>57</v>
@@ -3762,7 +3768,7 @@
         <v>9</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>58</v>
@@ -3771,21 +3777,21 @@
         <v>10</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>59</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>60</v>
@@ -3794,21 +3800,21 @@
         <v>10</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>61</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>62</v>
@@ -3817,12 +3823,12 @@
         <v>10</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>63</v>
@@ -3831,7 +3837,7 @@
         <v>9</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>64</v>
@@ -3840,21 +3846,21 @@
         <v>10</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>66</v>
@@ -3863,21 +3869,21 @@
         <v>10</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B147" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>68</v>
@@ -3886,21 +3892,21 @@
         <v>10</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B148" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>70</v>
@@ -3909,21 +3915,21 @@
         <v>10</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>71</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>72</v>
@@ -3932,21 +3938,21 @@
         <v>10</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B150" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>74</v>
@@ -3955,21 +3961,21 @@
         <v>10</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B151" s="2" t="s">
         <v>75</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>76</v>
@@ -3978,21 +3984,21 @@
         <v>10</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B152" s="2" t="s">
         <v>77</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>78</v>
@@ -4001,21 +4007,21 @@
         <v>10</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B153" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E153" s="2" t="s">
         <v>80</v>
@@ -4024,21 +4030,21 @@
         <v>10</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B154" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>82</v>
@@ -4047,21 +4053,21 @@
         <v>10</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B155" s="2" t="s">
         <v>83</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>84</v>
@@ -4070,21 +4076,21 @@
         <v>10</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>85</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>86</v>
@@ -4093,21 +4099,21 @@
         <v>10</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>88</v>
@@ -4116,21 +4122,21 @@
         <v>10</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B158" s="2" t="s">
         <v>89</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>90</v>
@@ -4139,21 +4145,21 @@
         <v>10</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B159" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E159" s="2" t="s">
         <v>92</v>
@@ -4162,21 +4168,21 @@
         <v>10</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B160" s="2" t="s">
         <v>93</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>94</v>
@@ -4185,21 +4191,21 @@
         <v>10</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B161" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E161" s="2" t="s">
         <v>96</v>
@@ -4208,21 +4214,21 @@
         <v>10</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>98</v>
@@ -4231,21 +4237,21 @@
         <v>10</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B163" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>100</v>
@@ -4254,12 +4260,12 @@
         <v>10</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B164" s="2" t="s">
         <v>101</v>
@@ -4268,7 +4274,7 @@
         <v>9</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>102</v>
@@ -4277,21 +4283,21 @@
         <v>10</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B165" s="2" t="s">
         <v>103</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E165" s="2" t="s">
         <v>104</v>
@@ -4300,21 +4306,21 @@
         <v>10</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B166" s="2" t="s">
         <v>105</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E166" s="2" t="s">
         <v>106</v>
@@ -4323,44 +4329,44 @@
         <v>10</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D167" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B167" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C167" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D167" s="2" t="s">
+      <c r="E167" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F167" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G167" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="E167" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F167" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G167" s="2" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E168" s="2" t="s">
         <v>54</v>
@@ -4369,21 +4375,21 @@
         <v>10</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B169" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E169" s="2" t="s">
         <v>56</v>
@@ -4392,12 +4398,12 @@
         <v>10</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B170" s="2" t="s">
         <v>57</v>
@@ -4406,7 +4412,7 @@
         <v>9</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>58</v>
@@ -4415,21 +4421,21 @@
         <v>10</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B171" s="2" t="s">
         <v>59</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E171" s="2" t="s">
         <v>60</v>
@@ -4438,21 +4444,21 @@
         <v>10</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B172" s="2" t="s">
         <v>61</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E172" s="2" t="s">
         <v>62</v>
@@ -4461,12 +4467,12 @@
         <v>10</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B173" s="2" t="s">
         <v>63</v>
@@ -4475,7 +4481,7 @@
         <v>9</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E173" s="2" t="s">
         <v>64</v>
@@ -4484,21 +4490,21 @@
         <v>10</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B174" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E174" s="2" t="s">
         <v>66</v>
@@ -4507,21 +4513,21 @@
         <v>10</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B175" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E175" s="2" t="s">
         <v>68</v>
@@ -4530,21 +4536,21 @@
         <v>10</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B176" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>70</v>
@@ -4553,21 +4559,21 @@
         <v>10</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B177" s="2" t="s">
         <v>71</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E177" s="2" t="s">
         <v>72</v>
@@ -4576,21 +4582,21 @@
         <v>10</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B178" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E178" s="2" t="s">
         <v>74</v>
@@ -4599,21 +4605,21 @@
         <v>10</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B179" s="2" t="s">
         <v>75</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E179" s="2" t="s">
         <v>76</v>
@@ -4622,21 +4628,21 @@
         <v>10</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B180" s="2" t="s">
         <v>77</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E180" s="2" t="s">
         <v>78</v>
@@ -4645,21 +4651,21 @@
         <v>10</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B181" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E181" s="2" t="s">
         <v>80</v>
@@ -4668,21 +4674,21 @@
         <v>10</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B182" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E182" s="2" t="s">
         <v>82</v>
@@ -4691,21 +4697,21 @@
         <v>10</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B183" s="2" t="s">
         <v>83</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E183" s="2" t="s">
         <v>84</v>
@@ -4714,21 +4720,21 @@
         <v>10</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B184" s="2" t="s">
         <v>85</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E184" s="2" t="s">
         <v>86</v>
@@ -4737,21 +4743,21 @@
         <v>10</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B185" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E185" s="2" t="s">
         <v>88</v>
@@ -4760,21 +4766,21 @@
         <v>10</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B186" s="2" t="s">
         <v>89</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E186" s="2" t="s">
         <v>90</v>
@@ -4783,21 +4789,21 @@
         <v>10</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B187" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E187" s="2" t="s">
         <v>92</v>
@@ -4806,21 +4812,21 @@
         <v>10</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B188" s="2" t="s">
         <v>93</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E188" s="2" t="s">
         <v>94</v>
@@ -4829,21 +4835,21 @@
         <v>10</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B189" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E189" s="2" t="s">
         <v>96</v>
@@ -4852,21 +4858,21 @@
         <v>10</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B190" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E190" s="2" t="s">
         <v>98</v>
@@ -4875,21 +4881,21 @@
         <v>10</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B191" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E191" s="2" t="s">
         <v>100</v>
@@ -4898,12 +4904,12 @@
         <v>10</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B192" s="2" t="s">
         <v>101</v>
@@ -4912,7 +4918,7 @@
         <v>9</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E192" s="2" t="s">
         <v>102</v>
@@ -4921,21 +4927,21 @@
         <v>10</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B193" s="2" t="s">
         <v>103</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E193" s="2" t="s">
         <v>104</v>
@@ -4944,21 +4950,21 @@
         <v>10</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B194" s="2" t="s">
         <v>105</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E194" s="2" t="s">
         <v>106</v>
@@ -4967,30 +4973,30 @@
         <v>10</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C195" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D195" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B195" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="C195" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D195" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="E195" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F195" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G195" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="F195" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G195" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="196">
@@ -4998,59 +5004,59 @@
         <v>131</v>
       </c>
       <c r="B196" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C196" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D196" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E196" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="C196" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D196" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E196" s="2" t="s">
-        <v>133</v>
-      </c>
       <c r="F196" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B197" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="B197" s="2" t="s">
+      <c r="C197" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D197" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E197" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="C197" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D197" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="E197" s="2" t="s">
-        <v>137</v>
-      </c>
       <c r="F197" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B198" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C198" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D198" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="C198" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D198" s="2" t="s">
-        <v>136</v>
       </c>
       <c r="E198" s="2" t="s">
         <v>139</v>
@@ -5059,21 +5065,21 @@
         <v>10</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B199" s="2" t="s">
         <v>140</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E199" s="2" t="s">
         <v>141</v>
@@ -5082,30 +5088,53 @@
         <v>10</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>24</v>
+        <v>142</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D200" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E200" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="F200" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G200" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="E200" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F200" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G200" s="2" t="s">
-        <v>16</v>
+      <c r="B201" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C201" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D201" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E201" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F201" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G201" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
